--- a/Data/Home/Kitchen.GasStove001.xlsx
+++ b/Data/Home/Kitchen.GasStove001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:I139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709270399</v>
+        <v>1711859650</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709272424</v>
+        <v>1711861559</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709330636</v>
+        <v>1711875899</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709332817</v>
+        <v>1711879703</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709343119</v>
+        <v>1711928182</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +681,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709344549</v>
+        <v>1711930054</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +699,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +718,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709346196</v>
+        <v>1712015552</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +736,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +755,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709347573</v>
+        <v>1712018486</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +773,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +792,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709352986</v>
+        <v>1712128212</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +810,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +833,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709356261</v>
+        <v>1712131415</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +851,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +870,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709417508</v>
+        <v>1712274811</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +888,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +911,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709419506</v>
+        <v>1712275899</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +929,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +948,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709439687</v>
+        <v>1712295973</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +966,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +989,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709443149</v>
+        <v>1712299644</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +1007,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1026,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709502780</v>
+        <v>1712306599</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1044,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1063,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709505465</v>
+        <v>1712308940</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1081,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1100,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709604501</v>
+        <v>1712374268</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1118,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1137,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709607311</v>
+        <v>1712378350</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1117,6 +1155,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1174,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709689129</v>
+        <v>1712386922</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1192,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1211,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709691172</v>
+        <v>1712389105</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1229,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1248,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709697149</v>
+        <v>1712389305</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1266,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1285,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709700340</v>
+        <v>1712389728</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1303,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1322,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709772208</v>
+        <v>1712461653</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1340,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1359,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709774122</v>
+        <v>1712464783</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1377,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1396,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709784099</v>
+        <v>1712467655</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1369,6 +1414,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1433,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709786367</v>
+        <v>1712470840</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1451,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1470,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709792637</v>
+        <v>1712472784</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1488,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1511,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709793149</v>
+        <v>1712475248</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1477,6 +1529,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1548,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709866511</v>
+        <v>1712495242</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1566,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1585,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709868126</v>
+        <v>1712497321</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1603,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1622,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709869951</v>
+        <v>1712533726</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1585,6 +1640,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1659,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709871753</v>
+        <v>1712536793</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,6 +1677,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1696,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709936521</v>
+        <v>1712551682</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1714,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1733,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709938085</v>
+        <v>1712555426</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1693,6 +1751,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1770,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709959507</v>
+        <v>1712555717</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1729,6 +1788,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1811,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709962142</v>
+        <v>1712558167</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1765,6 +1829,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1848,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1710039010</v>
+        <v>1712560216</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1866,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1885,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1710041248</v>
+        <v>1712562618</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1903,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1922,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1710125702</v>
+        <v>1712620148</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1940,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1963,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1710129243</v>
+        <v>1712622883</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +1981,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +2000,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1710133042</v>
+        <v>1712637090</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +2018,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2041,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1710134915</v>
+        <v>1712639240</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2059,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2078,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1710210590</v>
+        <v>1712726373</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2017,6 +2096,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2115,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1710212942</v>
+        <v>1712730086</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2053,6 +2133,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2152,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1710223205</v>
+        <v>1712791999</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2170,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2189,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1710225535</v>
+        <v>1712795261</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2125,6 +2207,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2226,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1710228710</v>
+        <v>1712811850</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2161,6 +2244,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2179,7 +2263,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1710231106</v>
+        <v>1712814017</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2197,6 +2281,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2300,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710308557</v>
+        <v>1712878686</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2233,6 +2318,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2337,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710311803</v>
+        <v>1712881940</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2269,6 +2355,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2287,7 +2374,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710332492</v>
+        <v>1712900354</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2305,6 +2392,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2323,7 +2415,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710334507</v>
+        <v>1712903458</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2341,6 +2433,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2452,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710381508</v>
+        <v>1712905759</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2377,6 +2470,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2493,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710383978</v>
+        <v>1712908840</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2413,6 +2511,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2530,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710390310</v>
+        <v>1712919405</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2449,6 +2548,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2567,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710392863</v>
+        <v>1712922033</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2485,6 +2585,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2503,7 +2604,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710410712</v>
+        <v>1712992218</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2521,6 +2622,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2539,7 +2641,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710412572</v>
+        <v>1712994509</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2557,6 +2659,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2575,7 +2678,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710456227</v>
+        <v>1713019486</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2593,6 +2696,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2611,7 +2719,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710458565</v>
+        <v>1713023247</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2629,6 +2737,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2647,7 +2756,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710473568</v>
+        <v>1713061492</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2665,6 +2774,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2683,7 +2797,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710475910</v>
+        <v>1713063981</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2701,6 +2815,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2719,7 +2834,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710627172</v>
+        <v>1713065554</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2737,6 +2852,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2755,7 +2871,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710629783</v>
+        <v>1713068882</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2773,6 +2889,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2791,7 +2908,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710642809</v>
+        <v>1713080086</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2809,6 +2926,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2827,7 +2945,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710644668</v>
+        <v>1713081877</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2845,6 +2963,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2863,7 +2982,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710664223</v>
+        <v>1713083252</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2881,6 +3000,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2899,7 +3019,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710666997</v>
+        <v>1713086763</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2917,6 +3037,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2935,7 +3056,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710730995</v>
+        <v>1713093445</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2953,6 +3074,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2971,7 +3093,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710733771</v>
+        <v>1713096645</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2989,6 +3111,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3007,7 +3130,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710799887</v>
+        <v>1713111902</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3025,6 +3148,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3043,7 +3171,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710801514</v>
+        <v>1713114767</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3061,6 +3189,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3079,7 +3208,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710825976</v>
+        <v>1713138445</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3097,6 +3226,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3115,7 +3249,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710828882</v>
+        <v>1713140114</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3133,6 +3267,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3151,7 +3286,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710895545</v>
+        <v>1713167767</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3169,6 +3304,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3187,7 +3327,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710898476</v>
+        <v>1713171092</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3205,6 +3345,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3223,7 +3364,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710913572</v>
+        <v>1713245026</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3241,6 +3382,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3259,7 +3401,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710916319</v>
+        <v>1713246812</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3277,6 +3419,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3295,7 +3438,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710931735</v>
+        <v>1713311284</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3313,6 +3456,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3331,7 +3479,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710933653</v>
+        <v>1713314706</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3349,6 +3497,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3367,7 +3516,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710986770</v>
+        <v>1713333197</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3385,6 +3534,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3403,7 +3557,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710989805</v>
+        <v>1713335799</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3421,6 +3575,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3439,7 +3594,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710996173</v>
+        <v>1713344164</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3457,6 +3612,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3475,7 +3631,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710998531</v>
+        <v>1713345025</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3493,6 +3649,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3511,7 +3668,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1711002922</v>
+        <v>1713422891</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3529,6 +3686,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3547,7 +3709,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1711004559</v>
+        <v>1713424824</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3565,6 +3727,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3583,7 +3746,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1711016628</v>
+        <v>1713430314</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3601,6 +3764,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3619,7 +3787,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1711019357</v>
+        <v>1713433078</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3637,6 +3805,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3655,7 +3824,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1711075976</v>
+        <v>1713483733</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3673,6 +3842,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3691,7 +3861,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1711077802</v>
+        <v>1713487128</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3709,6 +3879,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3727,7 +3898,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1711162543</v>
+        <v>1713517416</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3745,6 +3916,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3763,7 +3939,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1711164448</v>
+        <v>1713520101</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3781,6 +3957,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3799,7 +3976,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1711233793</v>
+        <v>1713584125</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3817,6 +3994,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3835,7 +4013,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1711236482</v>
+        <v>1713587765</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3853,6 +4031,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3871,7 +4050,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1711253047</v>
+        <v>1713600341</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3889,6 +4068,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3907,7 +4091,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1711256465</v>
+        <v>1713602240</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3925,6 +4109,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3943,7 +4128,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1711342929</v>
+        <v>1713606356</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3961,6 +4146,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3979,7 +4169,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1711345354</v>
+        <v>1713608269</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3997,6 +4187,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4015,7 +4206,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1711349856</v>
+        <v>1713629674</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4033,6 +4224,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4051,7 +4243,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1711352338</v>
+        <v>1713631803</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4069,6 +4261,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4087,7 +4280,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1711411055</v>
+        <v>1713670374</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4105,6 +4298,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4123,7 +4317,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1711413981</v>
+        <v>1713672492</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4141,6 +4335,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4159,7 +4354,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1711441811</v>
+        <v>1713677828</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4177,6 +4372,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4195,7 +4391,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1711444668</v>
+        <v>1713680194</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4213,6 +4409,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4231,7 +4428,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1711515201</v>
+        <v>1713680592</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4249,6 +4446,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4267,7 +4469,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1711516715</v>
+        <v>1713684146</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4285,6 +4487,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4303,7 +4506,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1711524150</v>
+        <v>1713710564</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4321,6 +4524,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4339,7 +4543,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1711528376</v>
+        <v>1713713140</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4357,6 +4561,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4375,7 +4580,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1711609926</v>
+        <v>1713829188</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4393,6 +4598,11 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4411,7 +4621,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1711613897</v>
+        <v>1713832517</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4429,6 +4639,1083 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1713916095</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: on</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1713918513</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: off</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1713945239</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: on</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1713947180</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: off</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1714002284</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: on</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1714005300</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: off</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1714021962</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: on</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1714025874</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: off</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1714034836</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: on</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1714037611</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: off</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1714088537</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: on</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1714091250</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: off</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1714110563</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: on</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1714112846</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: off</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1714192705</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: on</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1714194183</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: off</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1714202279</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: on</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1714206329</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: off</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1714234917</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: on</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1714238153</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: off</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1714276288</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: on</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1714278245</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: off</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1714286489</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: on</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1714288221</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: off</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1714290156</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: on</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1714291833</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: off</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1714299789</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: on</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>GasStove_Operation</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1714302922</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Kitchen.GasStove001.state: off</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
